--- a/data/trans_dic/CAGE_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,42 +717,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,72</t>
+          <t>0,25; 1,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,17</t>
+          <t>0,65; 2,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,15</t>
+          <t>0,45; 2,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,21</t>
+          <t>0,35; 2,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,17</t>
+          <t>0,26; 1,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,79</t>
+          <t>0,37; 1,85</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,48</t>
+          <t>0,31; 1,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,59</t>
+          <t>0,69; 2,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,41</t>
+          <t>1,35; 3,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,6</t>
+          <t>0,99; 3,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,81</t>
+          <t>0,09; 0,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,73</t>
+          <t>1,04; 5,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,79</t>
+          <t>0,2; 0,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,29</t>
+          <t>0,4; 1,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,89</t>
+          <t>0,79; 1,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,6</t>
+          <t>1,35; 3,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,88</t>
+          <t>0,4; 1,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,83</t>
+          <t>1,42; 3,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,96</t>
+          <t>0,42; 2,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,57</t>
+          <t>0,72; 3,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,97</t>
+          <t>0,22; 1,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,91</t>
+          <t>0,78; 1,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,97</t>
+          <t>0,2; 0,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,96</t>
+          <t>0,36; 2,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,6</t>
+          <t>0,35; 1,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,03</t>
+          <t>1,71; 4,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,16</t>
+          <t>0,68; 2,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,28</t>
+          <t>2,33; 6,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,65</t>
+          <t>0,36; 1,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,9</t>
+          <t>0,57; 1,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,25</t>
+          <t>0,35; 2,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,31</t>
+          <t>0,43; 1,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,02</t>
+          <t>0,93; 2,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,78</t>
+          <t>0,73; 1,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,36</t>
+          <t>1,74; 4,28</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,19</t>
+          <t>0,52; 1,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,51</t>
+          <t>1,46; 2,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,94</t>
+          <t>1,06; 1,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,1</t>
+          <t>1,65; 3,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,52</t>
+          <t>0,13; 0,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,79</t>
+          <t>0,28; 0,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,23</t>
+          <t>0,56; 2,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,73</t>
+          <t>0,36; 0,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,79; 1,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,23</t>
+          <t>0,73; 1,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,47</t>
+          <t>1,26; 2,49</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1063; 11942</t>
+          <t>1712; 11880</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4349; 15233</t>
+          <t>4601; 16329</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2585; 14537</t>
+          <t>3069; 14537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1159; 7351</t>
+          <t>1149; 7421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1896</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5048</t>
+          <t>0; 5178</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6577</t>
+          <t>0; 6633</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4992</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1061; 11311</t>
+          <t>1056; 11308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5102; 16895</t>
+          <t>4994; 16969</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4003; 15723</t>
+          <t>3483; 16221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2047; 8842</t>
+          <t>1845; 9122</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3083; 14211</t>
+          <t>2981; 13898</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7276; 26369</t>
+          <t>7021; 28224</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13863; 34906</t>
+          <t>13837; 35035</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4819; 17152</t>
+          <t>4716; 17390</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6810</t>
+          <t>0; 5762</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4953</t>
+          <t>0; 5987</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>927; 8425</t>
+          <t>933; 8074</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2254; 11474</t>
+          <t>2071; 11454</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3883; 15320</t>
+          <t>3919; 15854</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8292; 26491</t>
+          <t>8244; 27310</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15720; 39102</t>
+          <t>16367; 38599</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9158; 24362</t>
+          <t>9123; 24272</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2865; 12759</t>
+          <t>2713; 13258</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10677; 29002</t>
+          <t>10766; 29441</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3212; 14853</t>
+          <t>3219; 15304</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2278; 11463</t>
+          <t>2322; 11944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1884</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5206</t>
+          <t>0; 4999</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 14900</t>
+          <t>0; 14552</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2898; 13177</t>
+          <t>2937; 14500</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11260; 29383</t>
+          <t>11957; 30218</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3135; 15045</t>
+          <t>3166; 14902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2727; 20428</t>
+          <t>2503; 19400</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2990; 15097</t>
+          <t>3264; 15257</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16297; 38152</t>
+          <t>16180; 38727</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6914; 20290</t>
+          <t>6336; 20659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10149; 27800</t>
+          <t>10295; 28242</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3648; 17175</t>
+          <t>3691; 16754</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7604</t>
+          <t>0; 7470</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6096; 19784</t>
+          <t>5941; 20451</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1215; 6497</t>
+          <t>1011; 7141</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8795; 26019</t>
+          <t>8577; 26141</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17374; 40419</t>
+          <t>18597; 41076</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14971; 35202</t>
+          <t>14468; 35675</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12502; 31893</t>
+          <t>12694; 31318</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17045; 38902</t>
+          <t>17014; 38046</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50279; 85946</t>
+          <t>50005; 84334</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36392; 65896</t>
+          <t>36011; 65692</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24755; 48734</t>
+          <t>25905; 50138</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3720; 17659</t>
+          <t>4326; 18367</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1986; 11405</t>
+          <t>1989; 11445</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9745; 28031</t>
+          <t>9870; 27129</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5789; 22683</t>
+          <t>5657; 24072</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24809; 48344</t>
+          <t>24204; 47707</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55135; 91422</t>
+          <t>55382; 90084</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51351; 85316</t>
+          <t>50398; 83590</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34586; 64109</t>
+          <t>32694; 64580</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/CAGE_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,71</t>
+          <t>0,15; 1,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,32</t>
+          <t>0,61; 2,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,15</t>
+          <t>0,36; 1,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,23</t>
+          <t>0,34; 2,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,82</t>
+          <t>0,08; 0,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,21</t>
+          <t>0,36; 1,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,2</t>
+          <t>0,27; 1,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,85</t>
+          <t>0,36; 1,7</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,45</t>
+          <t>0,31; 1,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,77</t>
+          <t>0,65; 2,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,43</t>
+          <t>1,39; 3,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,65</t>
+          <t>0,84; 3,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,77</t>
+          <t>0,09; 0,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,72</t>
+          <t>1,14; 5,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,82</t>
+          <t>0,19; 0,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,33</t>
+          <t>0,36; 1,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,87</t>
+          <t>0,76; 1,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,59</t>
+          <t>1,24; 3,3</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,95</t>
+          <t>0,39; 1,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,89</t>
+          <t>1,45; 3,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,01</t>
+          <t>0,42; 1,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,72</t>
+          <t>1,22; 5,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,71; 7,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,06</t>
+          <t>0,2; 0,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,97</t>
+          <t>0,78; 1,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,96</t>
+          <t>0,21; 0,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,81</t>
+          <t>1,37; 4,51</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,62</t>
+          <t>0,36; 1,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,09</t>
+          <t>1,71; 4,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,2</t>
+          <t>0,73; 2,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,38</t>
+          <t>2,32; 6,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,61</t>
+          <t>0,31; 1,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,96</t>
+          <t>0,57; 1,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,47</t>
+          <t>0,65; 4,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,32</t>
+          <t>0,43; 1,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,05</t>
+          <t>0,91; 2,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,8</t>
+          <t>0,8; 1,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,28</t>
+          <t>1,97; 4,83</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,16</t>
+          <t>0,51; 1,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,46</t>
+          <t>1,45; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,94</t>
+          <t>1,06; 1,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,19</t>
+          <t>1,78; 3,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,54</t>
+          <t>0,14; 0,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,32</t>
+          <t>0,06; 0,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,77</t>
+          <t>0,26; 0,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,37</t>
+          <t>1,09; 3,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,72</t>
+          <t>0,38; 0,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,29</t>
+          <t>0,79; 1,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,2</t>
+          <t>0,74; 1,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,49</t>
+          <t>1,72; 2,89</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4527</t>
         </is>
       </c>
     </row>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1712; 11880</t>
+          <t>1058; 12474</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4601; 16329</t>
+          <t>4287; 15582</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3069; 14537</t>
+          <t>2396; 13185</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1149; 7421</t>
+          <t>1214; 7114</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5178</t>
+          <t>0; 5056</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6633</t>
+          <t>0; 6311</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4914</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1056; 11308</t>
+          <t>1060; 12730</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4994; 16969</t>
+          <t>5065; 17782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3483; 16221</t>
+          <t>3683; 16525</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1845; 9122</t>
+          <t>1913; 8945</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>15114</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2981; 13898</t>
+          <t>2967; 14128</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7021; 28224</t>
+          <t>6583; 25791</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13837; 35035</t>
+          <t>14224; 34870</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4716; 17390</t>
+          <t>4202; 16732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5762</t>
+          <t>0; 5810</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5987</t>
+          <t>0; 4899</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>933; 8074</t>
+          <t>928; 8599</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2071; 11454</t>
+          <t>2520; 12663</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3919; 15854</t>
+          <t>3587; 15113</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8244; 27310</t>
+          <t>7441; 27887</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16367; 38599</t>
+          <t>15760; 37583</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9123; 24272</t>
+          <t>8936; 23866</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>13940</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2713; 13258</t>
+          <t>2672; 12777</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10766; 29441</t>
+          <t>10949; 28853</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3219; 15304</t>
+          <t>3222; 14131</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2322; 11944</t>
+          <t>4313; 19256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4999</t>
+          <t>0; 5029</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2096,27 +2096,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 14552</t>
+          <t>1383; 15427</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2937; 14500</t>
+          <t>2791; 13368</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11957; 30218</t>
+          <t>12034; 30561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3166; 14902</t>
+          <t>3173; 14971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2503; 19400</t>
+          <t>7512; 24712</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>24277</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3264; 15257</t>
+          <t>3396; 15433</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16180; 38727</t>
+          <t>16176; 38264</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6336; 20659</t>
+          <t>6810; 20796</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10295; 28242</t>
+          <t>10796; 29144</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3691; 16754</t>
+          <t>3216; 16983</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7470</t>
+          <t>0; 6949</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5941; 20451</t>
+          <t>5986; 20689</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1011; 7141</t>
+          <t>2011; 13463</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8577; 26141</t>
+          <t>8593; 25547</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18597; 41076</t>
+          <t>18097; 40765</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14468; 35675</t>
+          <t>15932; 36500</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12694; 31318</t>
+          <t>15193; 37304</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>57858</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17014; 38046</t>
+          <t>16852; 37973</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50005; 84334</t>
+          <t>49698; 84873</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36011; 65692</t>
+          <t>36001; 64060</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25905; 50138</t>
+          <t>29825; 55525</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4326; 18367</t>
+          <t>4632; 18511</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1989; 11445</t>
+          <t>1979; 12225</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9870; 27129</t>
+          <t>9260; 26200</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5657; 24072</t>
+          <t>9748; 28483</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24204; 47707</t>
+          <t>24974; 48973</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55382; 90084</t>
+          <t>55520; 90574</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50398; 83590</t>
+          <t>51207; 83935</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32694; 64580</t>
+          <t>44071; 74386</t>
         </is>
       </c>
     </row>
